--- a/courses/poa/poa-lexicon.xlsx
+++ b/courses/poa/poa-lexicon.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="POA Lexicon" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="POA Lexicon" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="About" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -518,7 +518,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Appadurai's concept: the navigational ability to imagine and pursue alternative futures, developed through practice and social reinforcement. Not innate but cultivated through experience.</t>
+          <t>Arjun Appadurai's concept: the navigational ability to imagine and pursue alternative futures, developed through practice and social reinforcement. Not equally distributed—the poor have fewer opportunities to practice aspirational thinking.</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -545,7 +545,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Ray's framework: the cognitive range within which individuals set goals, shaped by reference groups and what they observe others achieving.</t>
+          <t>Debraj Ray's framework: the cognitive range within which individuals set goals, shaped by reference groups and perceived possibilities. A narrow window limits ambition; exposure to successful role models can expand it.</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>The distance between current status and aspirations. Optimal when moderate—close enough to seem achievable, far enough to require effort.</t>
+          <t>The distance between current status and aspiration level. Too small = complacency; too large = frustration and resignation. Optimal gap motivates effort.</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>When the gap between current status and aspirations is so large that effort seems pointless, leading to withdrawal of effort.</t>
+          <t>When aspirations are set too low (narrow window) or too high (frustration), leading to suboptimal investment in future-oriented behavior.</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Sen's framework: development should be measured by expansion of human capabilities—what people are able to do and be—not just income.</t>
+          <t>Amartya Sen's framework focusing on what people can do and be (functionings and capabilities), not just income or utility.</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>In Sen's framework: what people actually do and are—being well-nourished, being educated, participating in community life.</t>
+          <t>In Sen's framework: what people actually do and are—being well-nourished, being educated, participating in community, having self-respect.</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Economic concept where the same fundamentals can produce very different outcomes—some good (high equilibrium), some bad (poverty trap).</t>
+          <t>Same fundamentals can produce different stable outcomes—a key insight of development economics explaining persistent poverty.</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Self-reinforcing mechanism that keeps individuals or communities in poverty across generations despite resources or effort.</t>
+          <t>Self-reinforcing mechanism where poverty persists across generations through lack of capital, poor health, limited education, low aspirations.</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Risk event affecting entire communities simultaneously (drought, flood)—difficult to insure locally because everyone is hit together.</t>
+          <t>Risk event affecting entire communities simultaneously (drought, flood, price crash). Cannot be insured locally because everyone is hit together.</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Risk event affecting individual households (illness, job loss)—can potentially be smoothed through community networks.</t>
+          <t>Risk event affecting individual households (illness, job loss, death). Can potentially be insured within community through mutual support.</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Behavior adopted before shocks occur to reduce exposure—often involves choosing safer, lower-return options that perpetuate poverty.</t>
+          <t>Actions taken before shocks occur to reduce vulnerability: diversification, savings, avoiding risky investments. Often costly—'playing it safe' reduces income.</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>The value of having an option available, even if not used—NREGA's guarantee changes behavior even for non-participants.</t>
+          <t>The value of having an option available, even if not exercised. NREGA's guarantee changes behavior even for non-participants.</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Legal right of citizens to access government records. India's RTI Act (2005) is considered among the world's strongest.</t>
+          <t>RTI Act 2005 gives citizens the right to request information from public authorities, with 30-day response deadline and penalties for non-compliance.</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Public hearing format developed by MKSS where official records are read aloud and verified by affected citizens.</t>
+          <t>Public hearing format developed by MKSS where official records (especially muster rolls) are read aloud and verified by affected citizens.</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Mazdoor Kisan Shakti Sangathan—grassroots organization in Rajasthan that pioneered the RTI movement through innovative public accountability methods.</t>
+          <t>Mazdoor Kisan Shakti Sangathan—Rajasthan-based social movement that pioneered social audits and catalyzed national RTI law through grassroots activism.</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Designated official in each government department responsible for responding to RTI applications.</t>
+          <t>Designated official responsible for responding to RTI applications within 30 days. Faces personal penalties (₹250/day) for delays.</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Section 4 of RTI: government obligation to publish key information without waiting for requests.</t>
+          <t>RTI provision requiring government offices to publish key information without waiting for requests. Suo motu disclosure under Section 4.</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Quasi-judicial body (Central/State) that hears RTI appeals and can impose penalties on officials.</t>
+          <t>State and Central bodies (SIC, CIC) hearing second appeals and complaints. Can impose penalties and order disclosure.</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Mahatma Gandhi National Rural Employment Guarantee Act (2005): guarantees 100 days of wage employment per year to every rural household.</t>
+          <t>Mahatma Gandhi National Rural Employment Guarantee Act (2005). Guarantees 100 days of wage employment per year to every rural household willing to do unskilled manual work. The Act was repealed from 1 July 2026 and replaced by the Viksit Bharat G RAM G Act 2025, which raises the guarantee to 125 days.</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Program design where benefits are provided in response to citizen demand rather than administrative supply—NREGA's defining feature.</t>
+          <t>Program design where supply responds to citizen demand, with open-ended budgets. Contrast with supply-driven approaches with fixed allocations.</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Program design where conditions (manual labor at minimum wage) naturally select for intended beneficiaries without means-testing.</t>
+          <t>Program design where conditions (manual labor at minimum wage, 5km from home) naturally select intended beneficiaries without means-testing, reducing inclusion/exclusion errors.</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Official document issued to NREGA-registered households recording work demanded, provided, and wages paid.</t>
+          <t>Document registering a household under NREGA, recording days worked and wages earned. Essential for accessing employment guarantee.</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Official attendance record for NREGA worksites listing workers present each day—key document for accountability.</t>
+          <t>Official record of workers present at NREGA worksite each day. Key document for accountability; fake entries are common form of corruption.</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Public accountability mechanism where program records are verified by beneficiaries in open hearings—mandatory for NREGA.</t>
+          <t>Public accountability mechanism where program records are verified by beneficiaries in open hearings (gram sabha). Originated with MKSS in Rajasthan.</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Payment due to workers if work is not provided within 15 days of demand—rarely enforced in practice.</t>
+          <t>Cash compensation due when work is not provided within 15 days of application. Creates fiscal incentive for timely job provision.</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>NREGA requirement that 60% of expenditure must go to wages (not materials)—ensures labor intensity.</t>
+          <t>NREGA requires 60:40 ratio (wages to materials), ensuring program creates employment rather than enriching contractors.</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>2006 legislation recognizing rights of forest-dwelling communities over land they have traditionally cultivated.</t>
+          <t>Scheduled Tribes and Other Traditional Forest Dwellers (Recognition of Forest Rights) Act 2006. Recognizes individual and community rights over forest land and resources.</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>FRA provision: titles up to 4 hectares for families cultivating forest land before December 2005.</t>
+          <t>FRA provision recognizing rights of forest dwellers over land they've cultivated (up to 4 hectares) prior to December 2005.</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>FRA provision: village rights over common forest resources—minor forest produce, water bodies, grazing areas.</t>
+          <t>FRA provision recognizing community rights over common forest resources for collection, grazing, water, and traditional practices.</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>National Food Security Act (2013): legal entitlement to subsidized food grains covering ~800 million people.</t>
+          <t>National Food Security Act 2013—provides subsidized foodgrains to ~800 million people (75% rural, 50% urban) at ₹1-3/kg.</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>India's network of fair price shops distributing subsidized food grains to eligible households.</t>
+          <t>Government network of ~500,000 Fair Price Shops distributing subsidized food to ration card holders. Reformed through digitization and GPS tracking.</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Poorest of the poor category under PDS, entitled to 35 kg grain per household at highly subsidized rates.</t>
+          <t>PDS category for poorest of poor households, receiving 35kg/month at highest subsidy levels.</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Diversion of program benefits (grain, funds) away from intended beneficiaries—historically 40-50% in PDS.</t>
+          <t>Loss of PDS grains between procurement and beneficiary—historically 40-50%, now reduced to &lt;15% in reformed states.</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Movement driven by survival needs (drought, debt) rather than opportunity—often involves exploitation.</t>
+          <t>Forced movement seeking work during crisis—brick kilns, construction sites. Often involves entire families, children pulled from school, debt bondage.</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Framework where entitlements are justiciable legal rights, not discretionary benefits—enabling citizen claims against the state.</t>
+          <t>Framework where social protection entitlements are justiciable legal rights, not discretionary benefits. Citizens can claim against the state; officials face penalties for non-delivery.</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -2453,6 +2453,604 @@
           <t>11</t>
         </is>
       </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Behavioral Poverty Trap</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Poverty persists not just from resource constraints but from how poverty shapes psychology: reduced aspirations, shortened time horizons, depleted bandwidth.</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Aspiration Theory</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Mullainathan &amp; Shafir (2013)</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Voice</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>In Appadurai's framework, the ability to articulate aspirations, contest norms, and navigate bureaucratic systems. The poor often lack 'voice' due to social exclusion.</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Aspiration Theory</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Appadurai (2004)</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Terms of Recognition</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>The cultural context that shapes whose aspirations are seen as legitimate. Marginalized groups may have their aspirations dismissed or pathologized.</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Aspiration Theory</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Appadurai (2004)</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Agency</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>The ability to act on one's own values and objectives. Constrained by poverty, discrimination, lack of information, social norms.</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Development Theory</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>Sen (1999)</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Land Tenure Security</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Legal certainty over land rights that enables long-term investment, access to credit, and protection from eviction.</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Development Economics</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Development economics</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Coordination Failure</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>When optimal outcomes require simultaneous action by multiple actors, but no individual has incentive to move first.</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Development Economics</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Ray (1998)</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Zamindari Abolition</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Post-independence land reforms eliminating intermediary landlords. Partially successful—land often transferred to upper castes rather than tillers.</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Development History</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Indian land reform</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Lifecycle Risk</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>Predictable but costly life transitions: education expenses, marriage costs, old age dependency. Can be planned for if resources permit.</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Risk &amp; Insurance</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Risk economics</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Ex-Post Coping</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Actions taken after shocks to smooth consumption: selling assets, borrowing, reducing food intake, pulling children from school. Often has long-term costs.</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>Risk &amp; Insurance</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>Risk economics</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Asset Depletion</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Selling productive assets (livestock, land, tools) to cope with shocks. Creates poverty traps by reducing future income-generating capacity.</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Risk &amp; Insurance</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>Carter &amp; Barrett (2006)</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Function</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Social protection as risk mitigation: NREGA as unemployment insurance, PDS as food price insurance, health coverage as illness insurance.</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>Risk &amp; Insurance</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Social protection</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Political Economy</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Analysis of how political institutions, power relations, and interest groups shape economic policies and outcomes.</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>Political Economy</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Political science</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Justiciable Entitlement</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>A right that can be enforced through courts or administrative tribunals. NREGA's guarantee of employment is justiciable; many welfare schemes are not.</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>Rights Framework</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Legal theory</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>First Appellate Authority</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>Senior official to whom citizens can appeal if PIO denies information or fails to respond within 30 days.</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Rights Framework</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>RTI Act 2005</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Habitat Rights</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>FRA Section 3(1)(e)—rights of PVTGs (Particularly Vulnerable Tribal Groups) over their traditional habitats.</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>Rights Framework</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>FRA 2006</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Accountability Mechanism</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>Institutional features enabling citizens to hold officials responsible: RTI, social audits, grievance redressal, transparency provisions.</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>Accountability</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>Governance literature</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Citizen-State Interface</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Points of contact between citizens and government where rights are claimed, services delivered, and accountability exercised.</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>Accountability</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Governance literature</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Worksite Facility</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>NREGA mandates shade, drinking water, first aid, and crèche at worksites—addressing practical barriers to women's participation.</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>Program Design</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>NREGA Act 2005</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Permissible Works</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Schedule I and II of NREGA listing approved work categories: water conservation, drought-proofing, irrigation, land development, rural connectivity.</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>Program Design</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>NREGA Act 2005</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Priority Household (PHH)</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>NFSA category covering households not in AAY, receiving 5kg/person/month at subsidized rates.</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>Program Design</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>NFSA 2013</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Doorstep Delivery</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>PDS reform where grains are delivered directly to villages rather than requiring beneficiaries to travel to FPS, reducing diversion.</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>Program Design</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>Chhattisgarh model</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Mid-Day Meal</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>School feeding program providing cooked lunch to primary students, improving nutrition and enrollment. Now part of NFSA.</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>Program Design</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>NFSA 2013</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>ICDS</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Integrated Child Development Services—flagship nutrition program for children 0-6 and pregnant/lactating women through anganwadi centers.</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>Program Design</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>Indian social policy</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Implementation Gap</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>Difference between policy on paper and actual delivery. India's rights-based laws often face severe implementation gaps.</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>Implementation</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>Policy studies</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Person-Days</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>Standard unit measuring NREGA employment: one person working one day. Annual target measured in crore person-days generated.</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>Measurement</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>NREGA MIS</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Gram Sabha</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>Village assembly (all adult residents) that initiates and verifies FRA claims. Key democratic institution for local governance.</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>Political Institution</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>FRA 2006, PESA</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2498,7 +3096,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5">
